--- a/artfynd/A 47450-2024 artfynd.xlsx
+++ b/artfynd/A 47450-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150360</v>
       </c>
       <c r="B2" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150361</v>
+        <v>121150359</v>
       </c>
       <c r="B3" t="n">
-        <v>91957</v>
+        <v>91965</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712986</v>
+        <v>712729</v>
       </c>
       <c r="R3" t="n">
-        <v>7223523</v>
+        <v>7223601</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150359</v>
+        <v>121150361</v>
       </c>
       <c r="B4" t="n">
-        <v>91955</v>
+        <v>91967</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712729</v>
+        <v>712986</v>
       </c>
       <c r="R4" t="n">
-        <v>7223601</v>
+        <v>7223523</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 47450-2024 artfynd.xlsx
+++ b/artfynd/A 47450-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150360</v>
+        <v>121150361</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>91967</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712636</v>
+        <v>712986</v>
       </c>
       <c r="R2" t="n">
-        <v>7223655</v>
+        <v>7223523</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150361</v>
+        <v>121150360</v>
       </c>
       <c r="B4" t="n">
-        <v>91967</v>
+        <v>91973</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712986</v>
+        <v>712636</v>
       </c>
       <c r="R4" t="n">
-        <v>7223523</v>
+        <v>7223655</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1005,6 +1005,210 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121440251</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78627</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Maurlidengruvan, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>712620</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7223685</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Astrid Hedman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Astrid Hedman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121440287</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91973</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Maurlidengruvan, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>712652</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7223640</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Astrid Hedman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emmy Ransgart</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47450-2024 artfynd.xlsx
+++ b/artfynd/A 47450-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150361</v>
       </c>
       <c r="B2" t="n">
-        <v>91967</v>
+        <v>91979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150359</v>
+        <v>121150360</v>
       </c>
       <c r="B3" t="n">
-        <v>91965</v>
+        <v>91985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712729</v>
+        <v>712636</v>
       </c>
       <c r="R3" t="n">
-        <v>7223601</v>
+        <v>7223655</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150360</v>
+        <v>121150359</v>
       </c>
       <c r="B4" t="n">
-        <v>91973</v>
+        <v>91977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712636</v>
+        <v>712729</v>
       </c>
       <c r="R4" t="n">
-        <v>7223655</v>
+        <v>7223601</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,7 +1011,7 @@
         <v>121440251</v>
       </c>
       <c r="B5" t="n">
-        <v>78627</v>
+        <v>78630</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>121440287</v>
       </c>
       <c r="B6" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 47450-2024 artfynd.xlsx
+++ b/artfynd/A 47450-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150361</v>
       </c>
       <c r="B2" t="n">
-        <v>91979</v>
+        <v>91980</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150360</v>
+        <v>121150359</v>
       </c>
       <c r="B3" t="n">
-        <v>91985</v>
+        <v>91978</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712636</v>
+        <v>712729</v>
       </c>
       <c r="R3" t="n">
-        <v>7223655</v>
+        <v>7223601</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150359</v>
+        <v>121150360</v>
       </c>
       <c r="B4" t="n">
-        <v>91977</v>
+        <v>91986</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712729</v>
+        <v>712636</v>
       </c>
       <c r="R4" t="n">
-        <v>7223601</v>
+        <v>7223655</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1113,7 +1113,7 @@
         <v>121440287</v>
       </c>
       <c r="B6" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 47450-2024 artfynd.xlsx
+++ b/artfynd/A 47450-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150361</v>
+        <v>121150360</v>
       </c>
       <c r="B2" t="n">
-        <v>91980</v>
+        <v>91989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712986</v>
+        <v>712636</v>
       </c>
       <c r="R2" t="n">
-        <v>7223523</v>
+        <v>7223655</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,7 +789,7 @@
         <v>121150359</v>
       </c>
       <c r="B3" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150360</v>
+        <v>121150361</v>
       </c>
       <c r="B4" t="n">
-        <v>91986</v>
+        <v>91983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712636</v>
+        <v>712986</v>
       </c>
       <c r="R4" t="n">
-        <v>7223655</v>
+        <v>7223523</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,7 +1011,7 @@
         <v>121440251</v>
       </c>
       <c r="B5" t="n">
-        <v>78630</v>
+        <v>78633</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>121440287</v>
       </c>
       <c r="B6" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 47450-2024 artfynd.xlsx
+++ b/artfynd/A 47450-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150359</v>
+        <v>121150361</v>
       </c>
       <c r="B3" t="n">
-        <v>91981</v>
+        <v>91983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712729</v>
+        <v>712986</v>
       </c>
       <c r="R3" t="n">
-        <v>7223601</v>
+        <v>7223523</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150361</v>
+        <v>121150359</v>
       </c>
       <c r="B4" t="n">
-        <v>91983</v>
+        <v>91981</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712986</v>
+        <v>712729</v>
       </c>
       <c r="R4" t="n">
-        <v>7223523</v>
+        <v>7223601</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121440251</v>
+        <v>121525041</v>
       </c>
       <c r="B5" t="n">
-        <v>78633</v>
+        <v>91989</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712620</v>
+        <v>712652</v>
       </c>
       <c r="R5" t="n">
-        <v>7223685</v>
+        <v>7223640</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,12 +1078,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,22 +1108,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Astrid Hedman</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Astrid Hedman</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121440287</v>
+        <v>121525123</v>
       </c>
       <c r="B6" t="n">
-        <v>91989</v>
+        <v>78633</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,13 +1160,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712652</v>
+        <v>712620</v>
       </c>
       <c r="R6" t="n">
-        <v>7223640</v>
+        <v>7223685</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,9 +1193,19 @@
           <t>2024-08-27</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,12 +1220,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Astrid Hedman</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emmy Ransgart</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 47450-2024 artfynd.xlsx
+++ b/artfynd/A 47450-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>121525041</v>
       </c>
       <c r="B5" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>121525123</v>
       </c>
       <c r="B6" t="n">
-        <v>78633</v>
+        <v>78634</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 47450-2024 artfynd.xlsx
+++ b/artfynd/A 47450-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>121525041</v>
       </c>
       <c r="B5" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>121525123</v>
       </c>
       <c r="B6" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 47450-2024 artfynd.xlsx
+++ b/artfynd/A 47450-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121525041</v>
+        <v>121525123</v>
       </c>
       <c r="B5" t="n">
-        <v>91996</v>
+        <v>78642</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712652</v>
+        <v>712620</v>
       </c>
       <c r="R5" t="n">
-        <v>7223640</v>
+        <v>7223685</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121525123</v>
+        <v>121525041</v>
       </c>
       <c r="B6" t="n">
-        <v>78635</v>
+        <v>92004</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712620</v>
+        <v>712652</v>
       </c>
       <c r="R6" t="n">
-        <v>7223685</v>
+        <v>7223640</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
